--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_los_lagos.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_los_lagos.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-02 19:57</t>
+    <t xml:space="preserve">2026-08-05 10:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_los_lagos.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_los_lagos.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 10:54</t>
+    <t xml:space="preserve">2026-08-16 10:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_los_lagos.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_los_lagos.xlsx
@@ -42,7 +42,7 @@
     <t xml:space="preserve">Palena</t>
   </si>
   <si>
-    <t xml:space="preserve">Chiloe</t>
+    <t xml:space="preserve">Chiloé</t>
   </si>
   <si>
     <t xml:space="preserve">Básica</t>
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 10:02</t>
+    <t xml:space="preserve">2026-08-19 13:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_los_lagos.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_los_lagos.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 13:22</t>
+    <t xml:space="preserve">2026-08-28 12:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_los_lagos.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_los_lagos.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 12:01</t>
+    <t xml:space="preserve">2026-09-06 17:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
